--- a/apps/web/public/templates/student-bulk-import-template.xlsx
+++ b/apps/web/public/templates/student-bulk-import-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>First Name</t>
   </si>
@@ -19,6 +19,9 @@
     <t>Last Name</t>
   </si>
   <si>
+    <t>Class</t>
+  </si>
+  <si>
     <t>Email</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
   </si>
   <si>
     <t>DELETE-THIS-ROW</t>
+  </si>
+  <si>
+    <t>JSS 1A</t>
   </si>
   <si>
     <t/>
@@ -490,31 +496,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="26" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="26" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="26" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
+    <col min="1" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
+    <col min="18" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,77 +587,83 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="W2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>